--- a/backend/seeded_templates/Seeded_Products_Import.xlsx
+++ b/backend/seeded_templates/Seeded_Products_Import.xlsx
@@ -477,19 +477,19 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Premium Industrial Product Variant 1</v>
+        <v>Fe 550D TMT Rebar (12mm x 12m Bundles)</v>
       </c>
       <c r="B2" t="str">
-        <v>Fuel, Oil &amp; Gas</v>
+        <v>Steel &amp; Metal Products</v>
       </c>
       <c r="C2" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D2" t="str">
-        <v>High quality industrial product 1 with premium build. Ideal for heavy duty applications.</v>
+        <v>High-strength thermo-mechanically treated Fe 550D rebars with superior bendability, ductility, and seismic resistance for industrial RCC structures.</v>
       </c>
       <c r="E2">
-        <v>150</v>
+        <v>58500</v>
       </c>
       <c r="F2" t="str">
         <v>INR</v>
@@ -498,19 +498,19 @@
         <v>18</v>
       </c>
       <c r="H2" t="str">
-        <v>Nos</v>
+        <v>MT</v>
       </c>
       <c r="I2" t="str">
-        <v>HSN8001</v>
+        <v>721420</v>
       </c>
       <c r="J2" t="str">
-        <v>PROD-2026-1001</v>
+        <v>STEEL-TMT-550D-12</v>
       </c>
       <c r="K2" t="str">
-        <v>IndustrialBrand1</v>
+        <v>Jindal Panther / Tata Tiscon</v>
       </c>
       <c r="L2" t="str">
-        <v>MOD-PRO-1</v>
+        <v>FE-550D-12MM</v>
       </c>
       <c r="M2" t="str">
         <v>NEW</v>
@@ -519,22 +519,22 @@
         <v>Yes</v>
       </c>
       <c r="O2">
-        <v>180</v>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v/>
+        <v>62000</v>
+      </c>
+      <c r="P2">
+        <v>58500</v>
+      </c>
+      <c r="Q2">
+        <v>5.65</v>
       </c>
       <c r="R2" t="str">
-        <v>Special Offer</v>
+        <v>District Infrastructure Bulk Rate</v>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U2" t="str">
         <v>Yes</v>
@@ -543,27 +543,27 @@
         <v>10</v>
       </c>
       <c r="W2" t="str">
-        <v>https://images.unsplash.com/photo-1504917595217-d4dc5ebe6122, https://images.unsplash.com/photo-1530124566582-a618bc2615dc, https://images.unsplash.com/photo-1581092335397-9583eb92d232</v>
+        <v>https://images.unsplash.com/photo-1618090584176-7132b9911657?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X2" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Premium Industrial Product Variant 2</v>
+        <v>Industrial Safety Helmet Class-E with 6-Point Ratchet</v>
       </c>
       <c r="B3" t="str">
-        <v>Power &amp; Energy Equipment</v>
+        <v>Safety Equipment &amp; Industrial Safety</v>
       </c>
       <c r="C3" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D3" t="str">
-        <v>High quality industrial product 2 with premium build. Ideal for heavy duty applications.</v>
+        <v>High-density polyethylene (HDPE) electrical shock-proof safety helmet with 6-point nylon ratchet harness, chin strap, and sweatband.</v>
       </c>
       <c r="E3">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="F3" t="str">
         <v>INR</v>
@@ -575,16 +575,16 @@
         <v>Nos</v>
       </c>
       <c r="I3" t="str">
-        <v>HSN8002</v>
+        <v>650610</v>
       </c>
       <c r="J3" t="str">
-        <v>PROD-2026-1002</v>
+        <v>SAF-HLM-PRO-E</v>
       </c>
       <c r="K3" t="str">
-        <v>IndustrialBrand2</v>
+        <v>Karam / Udyogi</v>
       </c>
       <c r="L3" t="str">
-        <v>MOD-PRO-2</v>
+        <v>SHEL-E500</v>
       </c>
       <c r="M3" t="str">
         <v>NEW</v>
@@ -593,51 +593,51 @@
         <v>Yes</v>
       </c>
       <c r="O3">
-        <v>360</v>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
+        <v>550</v>
+      </c>
+      <c r="P3">
+        <v>450</v>
+      </c>
+      <c r="Q3">
+        <v>18.18</v>
       </c>
       <c r="R3" t="str">
-        <v>Special Offer</v>
+        <v>MSME Site Safety Special</v>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T3" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U3" t="str">
         <v>Yes</v>
       </c>
       <c r="V3">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="W3" t="str">
-        <v>https://images.unsplash.com/photo-1530124566582-a618bc2615dc, https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1581092795360-fd1ca04f0952</v>
+        <v>https://images.unsplash.com/photo-1581091226825-a6a2a5aee158?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X3" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Premium Industrial Product Variant 3</v>
+        <v>High-Pressure Carbon Steel Flanged Ball Valve (Class 300, 4-Inch)</v>
       </c>
       <c r="B4" t="str">
-        <v>Refractories</v>
+        <v>Pipes, Tiles &amp; Hardware</v>
       </c>
       <c r="C4" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D4" t="str">
-        <v>High quality industrial product 3 with premium build. Ideal for heavy duty applications.</v>
+        <v>Cast carbon steel two-piece full bore flanged ball valve designed for industrial steam, oil, water, and gas isolation pipelines.</v>
       </c>
       <c r="E4">
-        <v>450</v>
+        <v>9200</v>
       </c>
       <c r="F4" t="str">
         <v>INR</v>
@@ -649,16 +649,16 @@
         <v>Nos</v>
       </c>
       <c r="I4" t="str">
-        <v>HSN8003</v>
+        <v>848180</v>
       </c>
       <c r="J4" t="str">
-        <v>PROD-2026-1003</v>
+        <v>VALV-BV-CS-100</v>
       </c>
       <c r="K4" t="str">
-        <v>IndustrialBrand3</v>
+        <v>Audco / L&amp;T</v>
       </c>
       <c r="L4" t="str">
-        <v>MOD-PRO-3</v>
+        <v>FB-CS300-4IN</v>
       </c>
       <c r="M4" t="str">
         <v>NEW</v>
@@ -667,51 +667,51 @@
         <v>Yes</v>
       </c>
       <c r="O4">
-        <v>540</v>
-      </c>
-      <c r="P4" t="str">
-        <v/>
-      </c>
-      <c r="Q4" t="str">
-        <v/>
+        <v>10500</v>
+      </c>
+      <c r="P4">
+        <v>9200</v>
+      </c>
+      <c r="Q4">
+        <v>12.38</v>
       </c>
       <c r="R4" t="str">
-        <v>Special Offer</v>
+        <v>Plant Spares Special</v>
       </c>
       <c r="S4" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T4" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U4" t="str">
         <v>Yes</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W4" t="str">
-        <v>https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1581091226825-a6a2a5aee158, https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1504917595217-d4dc5ebe6122</v>
+        <v>https://images.unsplash.com/photo-1565043666747-69f6646db940?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X4" t="str">
-        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Premium Industrial Product Variant 4</v>
+        <v>3-Phase Squirrel Cage Induction Motor (15 HP / 11 kW, 1440 RPM)</v>
       </c>
       <c r="B5" t="str">
-        <v>Automobile Parts &amp; Services</v>
+        <v>Pumps, Motors &amp; Hydraulics</v>
       </c>
       <c r="C5" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D5" t="str">
-        <v>High quality industrial product 4 with premium build. Ideal for heavy duty applications.</v>
+        <v>Energy-efficient IE3 cast iron frame 3-phase induction motor with IP55 protection for severe industrial environments and continuous duty S1.</v>
       </c>
       <c r="E5">
-        <v>600</v>
+        <v>36800</v>
       </c>
       <c r="F5" t="str">
         <v>INR</v>
@@ -723,16 +723,16 @@
         <v>Nos</v>
       </c>
       <c r="I5" t="str">
-        <v>HSN8004</v>
+        <v>850152</v>
       </c>
       <c r="J5" t="str">
-        <v>PROD-2026-1004</v>
+        <v>MOT-IND-15HP-4P</v>
       </c>
       <c r="K5" t="str">
-        <v>IndustrialBrand4</v>
+        <v>Bharat Bijlee / ABB</v>
       </c>
       <c r="L5" t="str">
-        <v>MOD-PRO-4</v>
+        <v>IE3-160M-4P</v>
       </c>
       <c r="M5" t="str">
         <v>NEW</v>
@@ -741,51 +741,51 @@
         <v>Yes</v>
       </c>
       <c r="O5">
-        <v>720</v>
-      </c>
-      <c r="P5" t="str">
-        <v/>
-      </c>
-      <c r="Q5" t="str">
-        <v/>
+        <v>42000</v>
+      </c>
+      <c r="P5">
+        <v>36800</v>
+      </c>
+      <c r="Q5">
+        <v>12.38</v>
       </c>
       <c r="R5" t="str">
-        <v>Special Offer</v>
+        <v>Factory Modernization Offer</v>
       </c>
       <c r="S5" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T5" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U5" t="str">
         <v>Yes</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W5" t="str">
-        <v>https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1530124566582-a618bc2615dc, https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1581091226825-a6a2a5aee158</v>
+        <v>https://images.unsplash.com/photo-1581092160607-ee22621dd758?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X5" t="str">
-        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf, https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Premium Industrial Product Variant 5</v>
+        <v>1.1 kV XLPE 4-Core Aluminium Armoured Power Cable (185 sq.mm)</v>
       </c>
       <c r="B6" t="str">
-        <v>Office Equipment &amp; Stationery</v>
+        <v>Electrical Cables &amp; Power Equipment</v>
       </c>
       <c r="C6" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D6" t="str">
-        <v>High quality industrial product 5 with premium build. Ideal for heavy duty applications.</v>
+        <v>Heavy duty stranded aluminium conductor underground armoured power cable with cross-linked polyethylene (XLPE) insulation and galvanized steel strip armour.</v>
       </c>
       <c r="E6">
-        <v>750</v>
+        <v>1150</v>
       </c>
       <c r="F6" t="str">
         <v>INR</v>
@@ -794,19 +794,19 @@
         <v>18</v>
       </c>
       <c r="H6" t="str">
-        <v>Nos</v>
+        <v>Meter</v>
       </c>
       <c r="I6" t="str">
-        <v>HSN8005</v>
+        <v>854449</v>
       </c>
       <c r="J6" t="str">
-        <v>PROD-2026-1005</v>
+        <v>CBL-PWR-4C-185AL</v>
       </c>
       <c r="K6" t="str">
-        <v>IndustrialBrand5</v>
+        <v>Polycab / Havells</v>
       </c>
       <c r="L6" t="str">
-        <v>MOD-PRO-5</v>
+        <v>A2XFY-4X185</v>
       </c>
       <c r="M6" t="str">
         <v>NEW</v>
@@ -815,51 +815,51 @@
         <v>Yes</v>
       </c>
       <c r="O6">
-        <v>900</v>
-      </c>
-      <c r="P6" t="str">
-        <v/>
-      </c>
-      <c r="Q6" t="str">
-        <v/>
+        <v>1280</v>
+      </c>
+      <c r="P6">
+        <v>1150</v>
+      </c>
+      <c r="Q6">
+        <v>10.16</v>
       </c>
       <c r="R6" t="str">
-        <v>Special Offer</v>
+        <v>Substation Project Rate</v>
       </c>
       <c r="S6" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T6" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U6" t="str">
         <v>Yes</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="W6" t="str">
-        <v>https://images.unsplash.com/photo-1581091226825-a6a2a5aee158, https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1530124566582-a618bc2615dc</v>
+        <v>https://images.unsplash.com/photo-1621905251189-08b45d6a269e?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X6" t="str">
-        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf, https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Premium Industrial Product Variant 6</v>
+        <v>Grade 8.8 High-Tensile Hot-Dip Galvanized Hex Bolts &amp; Nuts (M16 x 80mm)</v>
       </c>
       <c r="B7" t="str">
-        <v>Bearings &amp; Mechanical Components</v>
+        <v>Industrial Fasteners &amp; Components</v>
       </c>
       <c r="C7" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D7" t="str">
-        <v>High quality industrial product 6 with premium build. Ideal for heavy duty applications.</v>
+        <v>Precision forged high-tensile structural bolts conforming to DIN 933 with matching heavy hex nuts and spring washers, hot-dip galvanized for corrosion resistance.</v>
       </c>
       <c r="E7">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="F7" t="str">
         <v>INR</v>
@@ -871,16 +871,16 @@
         <v>Nos</v>
       </c>
       <c r="I7" t="str">
-        <v>HSN8006</v>
+        <v>731815</v>
       </c>
       <c r="J7" t="str">
-        <v>PROD-2026-1006</v>
+        <v>FAS-HEX-M16-80</v>
       </c>
       <c r="K7" t="str">
-        <v>IndustrialBrand6</v>
+        <v>Sundram Fasteners / Unbrako</v>
       </c>
       <c r="L7" t="str">
-        <v>MOD-PRO-6</v>
+        <v>HDG-8.8-M16</v>
       </c>
       <c r="M7" t="str">
         <v>NEW</v>
@@ -889,51 +889,51 @@
         <v>Yes</v>
       </c>
       <c r="O7">
-        <v>1080</v>
-      </c>
-      <c r="P7" t="str">
-        <v/>
-      </c>
-      <c r="Q7" t="str">
-        <v/>
+        <v>55</v>
+      </c>
+      <c r="P7">
+        <v>48</v>
+      </c>
+      <c r="Q7">
+        <v>12.73</v>
       </c>
       <c r="R7" t="str">
-        <v>Special Offer</v>
+        <v>Bulk Erection Fasteners Deal</v>
       </c>
       <c r="S7" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T7" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U7" t="str">
         <v>Yes</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="W7" t="str">
-        <v>https://images.unsplash.com/photo-1581092795360-fd1ca04f0952, https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1581091226825-a6a2a5aee158</v>
+        <v>https://images.unsplash.com/photo-1581092795360-fd1ca04f0952?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X7" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Premium Industrial Product Variant 7</v>
+        <v>Deep Groove Ball Bearing 6312-2RS1/C3 (60x130x31 mm)</v>
       </c>
       <c r="B8" t="str">
-        <v>Construction &amp; Building Materials</v>
+        <v>Bearings &amp; Mechanical Components</v>
       </c>
       <c r="C8" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D8" t="str">
-        <v>High quality industrial product 7 with premium build. Ideal for heavy duty applications.</v>
+        <v>Single row deep groove ball bearing with C3 radial internal clearance and dual synthetic rubber contact seals on both sides for heavy industrial vibration duties.</v>
       </c>
       <c r="E8">
-        <v>1050</v>
+        <v>1850</v>
       </c>
       <c r="F8" t="str">
         <v>INR</v>
@@ -945,16 +945,16 @@
         <v>Nos</v>
       </c>
       <c r="I8" t="str">
-        <v>HSN8007</v>
+        <v>848210</v>
       </c>
       <c r="J8" t="str">
-        <v>PROD-2026-1007</v>
+        <v>BRG-DGB-6312-2RS</v>
       </c>
       <c r="K8" t="str">
-        <v>IndustrialBrand7</v>
+        <v>SKF / FAG</v>
       </c>
       <c r="L8" t="str">
-        <v>MOD-PRO-7</v>
+        <v>6312-2RS1-C3</v>
       </c>
       <c r="M8" t="str">
         <v>NEW</v>
@@ -963,22 +963,22 @@
         <v>Yes</v>
       </c>
       <c r="O8">
-        <v>1260</v>
-      </c>
-      <c r="P8" t="str">
-        <v/>
-      </c>
-      <c r="Q8" t="str">
-        <v/>
+        <v>2100</v>
+      </c>
+      <c r="P8">
+        <v>1850</v>
+      </c>
+      <c r="Q8">
+        <v>11.9</v>
       </c>
       <c r="R8" t="str">
-        <v>Special Offer</v>
+        <v>Original Spares Assured</v>
       </c>
       <c r="S8" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T8" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U8" t="str">
         <v>Yes</v>
@@ -987,27 +987,27 @@
         <v>10</v>
       </c>
       <c r="W8" t="str">
-        <v>https://images.unsplash.com/photo-1581092795360-fd1ca04f0952, https://images.unsplash.com/photo-1504917595217-d4dc5ebe6122, https://images.unsplash.com/photo-1581091226825-a6a2a5aee158, https://images.unsplash.com/photo-1530124566582-a618bc2615dc</v>
+        <v>https://images.unsplash.com/photo-1581092334651-ddf26d9a09d0?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X8" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Premium Industrial Product Variant 8</v>
+        <v>Double-Acting Heavy Duty Industrial Hydraulic Cylinder (100mm Bore x 400mm Stroke)</v>
       </c>
       <c r="B9" t="str">
-        <v>Steel &amp; Metal Products</v>
+        <v>Hydraulics &amp; Pneumatics</v>
       </c>
       <c r="C9" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D9" t="str">
-        <v>High quality industrial product 8 with premium build. Ideal for heavy duty applications.</v>
+        <v>Tie-rod industrial hydraulic ram cylinder engineered for 210 bar working pressure with hard chrome plated rod and imported polyurethane chevron seals.</v>
       </c>
       <c r="E9">
-        <v>1200</v>
+        <v>26500</v>
       </c>
       <c r="F9" t="str">
         <v>INR</v>
@@ -1019,16 +1019,16 @@
         <v>Nos</v>
       </c>
       <c r="I9" t="str">
-        <v>HSN8008</v>
+        <v>841221</v>
       </c>
       <c r="J9" t="str">
-        <v>PROD-2026-1008</v>
+        <v>HYD-CYL-100-400</v>
       </c>
       <c r="K9" t="str">
-        <v>IndustrialBrand8</v>
+        <v>Yuken / Rexroth MSME Partner</v>
       </c>
       <c r="L9" t="str">
-        <v>MOD-PRO-8</v>
+        <v>HC-210B-100-400</v>
       </c>
       <c r="M9" t="str">
         <v>NEW</v>
@@ -1037,72 +1037,72 @@
         <v>Yes</v>
       </c>
       <c r="O9">
-        <v>1440</v>
-      </c>
-      <c r="P9" t="str">
-        <v/>
-      </c>
-      <c r="Q9" t="str">
-        <v/>
+        <v>31000</v>
+      </c>
+      <c r="P9">
+        <v>26500</v>
+      </c>
+      <c r="Q9">
+        <v>14.52</v>
       </c>
       <c r="R9" t="str">
-        <v>Special Offer</v>
+        <v>Hydraulics Manufacturer Special</v>
       </c>
       <c r="S9" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T9" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U9" t="str">
         <v>Yes</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W9" t="str">
-        <v>https://images.unsplash.com/photo-1530124566582-a618bc2615dc, https://images.unsplash.com/photo-1581092795360-fd1ca04f0952, https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1581091226825-a6a2a5aee158</v>
+        <v>https://images.unsplash.com/photo-1581092162384-8987c1d64718?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X9" t="str">
-        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf, https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Premium Industrial Product Variant 9</v>
+        <v>Portland Slag Cement (PSC) 50 Kg Moisture-Proof Bags</v>
       </c>
       <c r="B10" t="str">
-        <v>FMCG &amp; Daily Utility Supply</v>
+        <v>Cement &amp; Concrete Products</v>
       </c>
       <c r="C10" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D10" t="str">
-        <v>High quality industrial product 9 with premium build. Ideal for heavy duty applications.</v>
+        <v>High performance slag cement manufactured with high glass content granulated blast furnace slag. Exceptional resistance to chemical and sulphate attack.</v>
       </c>
       <c r="E10">
-        <v>1350</v>
+        <v>345</v>
       </c>
       <c r="F10" t="str">
         <v>INR</v>
       </c>
       <c r="G10">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H10" t="str">
-        <v>Nos</v>
+        <v>Bags</v>
       </c>
       <c r="I10" t="str">
-        <v>HSN8009</v>
+        <v>252329</v>
       </c>
       <c r="J10" t="str">
-        <v>PROD-2026-1009</v>
+        <v>CEM-PSC-50KG</v>
       </c>
       <c r="K10" t="str">
-        <v>IndustrialBrand9</v>
+        <v>UltraTech / Dalmia</v>
       </c>
       <c r="L10" t="str">
-        <v>MOD-PRO-9</v>
+        <v>PSC-IS455</v>
       </c>
       <c r="M10" t="str">
         <v>NEW</v>
@@ -1111,51 +1111,51 @@
         <v>Yes</v>
       </c>
       <c r="O10">
-        <v>1620</v>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
-        <v/>
+        <v>380</v>
+      </c>
+      <c r="P10">
+        <v>345</v>
+      </c>
+      <c r="Q10">
+        <v>9.21</v>
       </c>
       <c r="R10" t="str">
-        <v>Special Offer</v>
+        <v>Construction Bulk Depot Price</v>
       </c>
       <c r="S10" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T10" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U10" t="str">
         <v>Yes</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="W10" t="str">
-        <v>https://images.unsplash.com/photo-1581091226825-a6a2a5aee158, https://images.unsplash.com/photo-1504917595217-d4dc5ebe6122, https://images.unsplash.com/photo-1581092335397-9583eb92d232</v>
+        <v>https://images.unsplash.com/photo-1587293852726-70cdb56c2866?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X10" t="str">
-        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf, https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Premium Industrial Product Variant 10</v>
+        <v>IGBT Multi-Process Inverter Welding Machine (400 Amp, 3-Phase)</v>
       </c>
       <c r="B11" t="str">
-        <v>teeeeeee</v>
+        <v>Welding &amp; Cutting Equipment</v>
       </c>
       <c r="C11" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D11" t="str">
-        <v>High quality industrial product 10 with premium build. Ideal for heavy duty applications.</v>
+        <v>Heavy duty digital industrial MMA/TIG inverter arc welding machine with thermal overload protection, arc force adjustment, and anti-stick features.</v>
       </c>
       <c r="E11">
-        <v>1500</v>
+        <v>32000</v>
       </c>
       <c r="F11" t="str">
         <v>INR</v>
@@ -1167,16 +1167,16 @@
         <v>Nos</v>
       </c>
       <c r="I11" t="str">
-        <v>HSN8010</v>
+        <v>851539</v>
       </c>
       <c r="J11" t="str">
-        <v>PROD-2026-1010</v>
+        <v>WELD-INV-400A-3P</v>
       </c>
       <c r="K11" t="str">
-        <v>IndustrialBrand10</v>
+        <v>ESAB / Ador Welding</v>
       </c>
       <c r="L11" t="str">
-        <v>MOD-PRO-10</v>
+        <v>ARC-400-IGBT</v>
       </c>
       <c r="M11" t="str">
         <v>NEW</v>
@@ -1185,51 +1185,51 @@
         <v>Yes</v>
       </c>
       <c r="O11">
-        <v>1800</v>
-      </c>
-      <c r="P11" t="str">
-        <v/>
-      </c>
-      <c r="Q11" t="str">
-        <v/>
+        <v>37500</v>
+      </c>
+      <c r="P11">
+        <v>32000</v>
+      </c>
+      <c r="Q11">
+        <v>14.67</v>
       </c>
       <c r="R11" t="str">
-        <v>Special Offer</v>
+        <v>Fabrication Workshop Kit</v>
       </c>
       <c r="S11" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T11" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U11" t="str">
         <v>Yes</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W11" t="str">
-        <v>https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1581091226825-a6a2a5aee158, https://images.unsplash.com/photo-1530124566582-a618bc2615dc</v>
+        <v>https://images.unsplash.com/photo-1581092583537-20d51b4b4f1b?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X11" t="str">
-        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf, https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Premium Industrial Product Variant 11</v>
+        <v>High Alumina 70% Industrial Refractory Fire Bricks (IS 8 Standard)</v>
       </c>
       <c r="B12" t="str">
-        <v>Industrial Chemicals</v>
+        <v>Refractories</v>
       </c>
       <c r="C12" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D12" t="str">
-        <v>High quality industrial product 11 with premium build. Ideal for heavy duty applications.</v>
+        <v>High-density Al2O3 refractory bricks for blast furnaces, steel reheating furnaces, rotary kilns, and high-temperature thermal power incinerators.</v>
       </c>
       <c r="E12">
-        <v>1650</v>
+        <v>72</v>
       </c>
       <c r="F12" t="str">
         <v>INR</v>
@@ -1241,16 +1241,16 @@
         <v>Nos</v>
       </c>
       <c r="I12" t="str">
-        <v>HSN8011</v>
+        <v>690220</v>
       </c>
       <c r="J12" t="str">
-        <v>PROD-2026-1011</v>
+        <v>REF-BRK-HA70-IS8</v>
       </c>
       <c r="K12" t="str">
-        <v>IndustrialBrand11</v>
+        <v>TRL Krosaki / RHI Magnesita</v>
       </c>
       <c r="L12" t="str">
-        <v>MOD-PRO-11</v>
+        <v>HA-70-STD</v>
       </c>
       <c r="M12" t="str">
         <v>NEW</v>
@@ -1259,72 +1259,72 @@
         <v>Yes</v>
       </c>
       <c r="O12">
-        <v>1980</v>
-      </c>
-      <c r="P12" t="str">
-        <v/>
-      </c>
-      <c r="Q12" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="P12">
+        <v>72</v>
+      </c>
+      <c r="Q12">
+        <v>15.29</v>
       </c>
       <c r="R12" t="str">
-        <v>Special Offer</v>
+        <v>Thermal Kiln Maintenance Special</v>
       </c>
       <c r="S12" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T12" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U12" t="str">
         <v>Yes</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="W12" t="str">
-        <v>https://images.unsplash.com/photo-1581091226825-a6a2a5aee158, https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1530124566582-a618bc2615dc, https://images.unsplash.com/photo-1581092795360-fd1ca04f0952</v>
+        <v>https://images.unsplash.com/photo-1587293852726-70cdb56c2866?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X12" t="str">
-        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Premium Industrial Product Variant 12</v>
+        <v>Authentic Sambalpuri Handloom Pure Cotton Ikat Saree (GI Certified)</v>
       </c>
       <c r="B13" t="str">
-        <v>Electrical Cables &amp; Power Equipment</v>
+        <v>Textile &amp; Garments Supply</v>
       </c>
       <c r="C13" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D13" t="str">
-        <v>High quality industrial product 12 with premium build. Ideal for heavy duty applications.</v>
+        <v>Traditional handcrafted Sambalpuri cotton saree produced by registered Odisha SHG weavers with intricate tie-and-dye Ikat floral border and pallu.</v>
       </c>
       <c r="E13">
-        <v>1800</v>
+        <v>3400</v>
       </c>
       <c r="F13" t="str">
         <v>INR</v>
       </c>
       <c r="G13">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H13" t="str">
         <v>Nos</v>
       </c>
       <c r="I13" t="str">
-        <v>HSN8012</v>
+        <v>520852</v>
       </c>
       <c r="J13" t="str">
-        <v>PROD-2026-1012</v>
+        <v>SHG-SAM-SAREE-01</v>
       </c>
       <c r="K13" t="str">
-        <v>IndustrialBrand12</v>
+        <v>Boyanika / Odisha Weavers Federation</v>
       </c>
       <c r="L13" t="str">
-        <v>MOD-PRO-12</v>
+        <v>SAM-IKAT-100C</v>
       </c>
       <c r="M13" t="str">
         <v>NEW</v>
@@ -1333,22 +1333,22 @@
         <v>Yes</v>
       </c>
       <c r="O13">
-        <v>2160</v>
-      </c>
-      <c r="P13" t="str">
-        <v/>
-      </c>
-      <c r="Q13" t="str">
-        <v/>
+        <v>4200</v>
+      </c>
+      <c r="P13">
+        <v>3400</v>
+      </c>
+      <c r="Q13">
+        <v>19.05</v>
       </c>
       <c r="R13" t="str">
-        <v>Special Offer</v>
+        <v>herSHG Artisan Direct Fair</v>
       </c>
       <c r="S13" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T13" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U13" t="str">
         <v>Yes</v>
@@ -1357,24 +1357,24 @@
         <v>10</v>
       </c>
       <c r="W13" t="str">
-        <v>https://images.unsplash.com/photo-1581092795360-fd1ca04f0952, https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1530124566582-a618bc2615dc</v>
+        <v>https://images.unsplash.com/photo-1610030469983-98e550d6193c?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X13" t="str">
-        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf, https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Premium Industrial Product Variant 13</v>
+        <v>Odisha Dhokra Brass Lost-Wax Casting Tribal Art Figurine (8-Inch)</v>
       </c>
       <c r="B14" t="str">
-        <v>Industrial Consumables</v>
+        <v>FMCG &amp; Daily Utility Supply</v>
       </c>
       <c r="C14" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D14" t="str">
-        <v>High quality industrial product 13 with premium build. Ideal for heavy duty applications.</v>
+        <v>Handmade bell-metal non-ferrous casting made by tribal artisan self-help groups using ancient lost-wax technique. Ideal for corporate gifts &amp; mementos.</v>
       </c>
       <c r="E14">
         <v>1950</v>
@@ -1383,22 +1383,22 @@
         <v>INR</v>
       </c>
       <c r="G14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H14" t="str">
         <v>Nos</v>
       </c>
       <c r="I14" t="str">
-        <v>HSN8013</v>
+        <v>830629</v>
       </c>
       <c r="J14" t="str">
-        <v>PROD-2026-1013</v>
+        <v>SHG-DHK-FIG-08</v>
       </c>
       <c r="K14" t="str">
-        <v>IndustrialBrand13</v>
+        <v>Utkalika / Tribal SHG Federation</v>
       </c>
       <c r="L14" t="str">
-        <v>MOD-PRO-13</v>
+        <v>DHOKRA-8IN</v>
       </c>
       <c r="M14" t="str">
         <v>NEW</v>
@@ -1407,51 +1407,51 @@
         <v>Yes</v>
       </c>
       <c r="O14">
-        <v>2340</v>
-      </c>
-      <c r="P14" t="str">
-        <v/>
-      </c>
-      <c r="Q14" t="str">
-        <v/>
+        <v>2400</v>
+      </c>
+      <c r="P14">
+        <v>1950</v>
+      </c>
+      <c r="Q14">
+        <v>18.75</v>
       </c>
       <c r="R14" t="str">
-        <v>Special Offer</v>
+        <v>Tribal Handicrafts Promotion</v>
       </c>
       <c r="S14" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T14" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U14" t="str">
         <v>Yes</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="W14" t="str">
-        <v>https://images.unsplash.com/photo-1530124566582-a618bc2615dc, https://images.unsplash.com/photo-1581092795360-fd1ca04f0952, https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1581091226825-a6a2a5aee158</v>
+        <v>https://images.unsplash.com/photo-1590736704728-f4730bb30770?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X14" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Premium Industrial Product Variant 14</v>
+        <v>Industrial Heavy Duty Nitrile Chemical Gauntlet Gloves (15-Inch, 15 Mil)</v>
       </c>
       <c r="B15" t="str">
-        <v>IT &amp; Computer Equipment</v>
+        <v>Safety Equipment &amp; Industrial Safety</v>
       </c>
       <c r="C15" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D15" t="str">
-        <v>High quality industrial product 14 with premium build. Ideal for heavy duty applications.</v>
+        <v>Flock-lined green nitrile gloves offering premium resistance against corrosive acids, caustic solvents, oils, and grease in chemical plants and refineries.</v>
       </c>
       <c r="E15">
-        <v>2100</v>
+        <v>240</v>
       </c>
       <c r="F15" t="str">
         <v>INR</v>
@@ -1460,19 +1460,19 @@
         <v>18</v>
       </c>
       <c r="H15" t="str">
-        <v>Nos</v>
+        <v>Pair</v>
       </c>
       <c r="I15" t="str">
-        <v>HSN8014</v>
+        <v>401519</v>
       </c>
       <c r="J15" t="str">
-        <v>PROD-2026-1014</v>
+        <v>SAF-GLV-NIT-15</v>
       </c>
       <c r="K15" t="str">
-        <v>IndustrialBrand14</v>
+        <v>Ansell / Honeywell</v>
       </c>
       <c r="L15" t="str">
-        <v>MOD-PRO-14</v>
+        <v>SOLVEX-15M</v>
       </c>
       <c r="M15" t="str">
         <v>NEW</v>
@@ -1481,51 +1481,51 @@
         <v>Yes</v>
       </c>
       <c r="O15">
-        <v>2520</v>
-      </c>
-      <c r="P15" t="str">
-        <v/>
-      </c>
-      <c r="Q15" t="str">
-        <v/>
+        <v>290</v>
+      </c>
+      <c r="P15">
+        <v>240</v>
+      </c>
+      <c r="Q15">
+        <v>17.24</v>
       </c>
       <c r="R15" t="str">
-        <v>Special Offer</v>
+        <v>PPE Bulk Deal</v>
       </c>
       <c r="S15" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T15" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U15" t="str">
         <v>Yes</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="W15" t="str">
-        <v>https://images.unsplash.com/photo-1581092795360-fd1ca04f0952, https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1581092335397-9583eb92d232</v>
+        <v>https://images.unsplash.com/photo-1581091226825-a6a2a5aee158?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X15" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Premium Industrial Product Variant 15</v>
+        <v>Heat-Resistant EP Rubber Conveyor Belt (EP 400/3, 800mm Wide)</v>
       </c>
       <c r="B16" t="str">
-        <v>Tools &amp; Industrial Hardware</v>
+        <v>Conveyor &amp; Material Handling Equipment</v>
       </c>
       <c r="C16" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D16" t="str">
-        <v>High quality industrial product 15 with premium build. Ideal for heavy duty applications.</v>
+        <v>Heavy duty multi-ply rubber conveyor belting with polyester warp and polyamide weft fabric for transporting coal, clinker, limestone, and ore.</v>
       </c>
       <c r="E16">
-        <v>2250</v>
+        <v>2600</v>
       </c>
       <c r="F16" t="str">
         <v>INR</v>
@@ -1534,19 +1534,19 @@
         <v>18</v>
       </c>
       <c r="H16" t="str">
-        <v>Nos</v>
+        <v>Meter</v>
       </c>
       <c r="I16" t="str">
-        <v>HSN8015</v>
+        <v>401012</v>
       </c>
       <c r="J16" t="str">
-        <v>PROD-2026-1015</v>
+        <v>CNV-BLT-EP400-800</v>
       </c>
       <c r="K16" t="str">
-        <v>IndustrialBrand15</v>
+        <v>Dunlop / Fenner</v>
       </c>
       <c r="L16" t="str">
-        <v>MOD-PRO-15</v>
+        <v>EP400-3PLY-HR</v>
       </c>
       <c r="M16" t="str">
         <v>NEW</v>
@@ -1555,51 +1555,51 @@
         <v>Yes</v>
       </c>
       <c r="O16">
-        <v>2700</v>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
-        <v/>
+        <v>3000</v>
+      </c>
+      <c r="P16">
+        <v>2600</v>
+      </c>
+      <c r="Q16">
+        <v>13.33</v>
       </c>
       <c r="R16" t="str">
-        <v>Special Offer</v>
+        <v>Bulk Mining Conveyor Discount</v>
       </c>
       <c r="S16" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T16" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U16" t="str">
         <v>Yes</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="W16" t="str">
-        <v>https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1581091226825-a6a2a5aee158, https://images.unsplash.com/photo-1504917595217-d4dc5ebe6122</v>
+        <v>https://images.unsplash.com/photo-1586528116311-ad8dd3c8310d?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X16" t="str">
-        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf, https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Premium Industrial Product Variant 16</v>
+        <v>Technical Grade Caustic Soda Flakes / Sodium Hydroxide (99.5% Pure, 50kg)</v>
       </c>
       <c r="B17" t="str">
-        <v>Furniture &amp; Interior Supplies</v>
+        <v>Industrial Chemicals</v>
       </c>
       <c r="C17" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D17" t="str">
-        <v>High quality industrial product 16 with premium build. Ideal for heavy duty applications.</v>
+        <v>High-purity sodium hydroxide flakes used extensively in alumina refining, water treatment, paper manufacturing, and textile effluent neutralization.</v>
       </c>
       <c r="E17">
-        <v>2400</v>
+        <v>2850</v>
       </c>
       <c r="F17" t="str">
         <v>INR</v>
@@ -1608,19 +1608,19 @@
         <v>18</v>
       </c>
       <c r="H17" t="str">
-        <v>Nos</v>
+        <v>Bags</v>
       </c>
       <c r="I17" t="str">
-        <v>HSN8016</v>
+        <v>281511</v>
       </c>
       <c r="J17" t="str">
-        <v>PROD-2026-1016</v>
+        <v>CHM-CS-FLK-50KG</v>
       </c>
       <c r="K17" t="str">
-        <v>IndustrialBrand16</v>
+        <v>GACL / DCM Shriram</v>
       </c>
       <c r="L17" t="str">
-        <v>MOD-PRO-16</v>
+        <v>NaOH-99.5-FLK</v>
       </c>
       <c r="M17" t="str">
         <v>NEW</v>
@@ -1629,72 +1629,72 @@
         <v>Yes</v>
       </c>
       <c r="O17">
-        <v>2880</v>
-      </c>
-      <c r="P17" t="str">
-        <v/>
-      </c>
-      <c r="Q17" t="str">
-        <v/>
+        <v>3200</v>
+      </c>
+      <c r="P17">
+        <v>2850</v>
+      </c>
+      <c r="Q17">
+        <v>10.94</v>
       </c>
       <c r="R17" t="str">
-        <v>Special Offer</v>
+        <v>Chemical Bulk Tanker / Bagged Deal</v>
       </c>
       <c r="S17" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T17" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U17" t="str">
         <v>Yes</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="W17" t="str">
-        <v>https://images.unsplash.com/photo-1581091226825-a6a2a5aee158, https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1530124566582-a618bc2615dc, https://images.unsplash.com/photo-1504917595217-d4dc5ebe6122</v>
+        <v>https://images.unsplash.com/photo-1587293852726-70cdb56c2866?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X17" t="str">
-        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Premium Industrial Product Variant 17</v>
+        <v>Heavy Duty Mining Dumper Radial Tyre (10.00 R20 16PR All-Steel)</v>
       </c>
       <c r="B18" t="str">
-        <v>General Industrial Supplier</v>
+        <v>Tyres &amp; Rubber Products</v>
       </c>
       <c r="C18" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D18" t="str">
-        <v>High quality industrial product 17 with premium build. Ideal for heavy duty applications.</v>
+        <v>All-steel radial commercial truck and dumper tyre engineered with stone-ejecting grooves and chip-resistant tread compound for rough quarry mining roads.</v>
       </c>
       <c r="E18">
-        <v>2550</v>
+        <v>22800</v>
       </c>
       <c r="F18" t="str">
         <v>INR</v>
       </c>
       <c r="G18">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H18" t="str">
         <v>Nos</v>
       </c>
       <c r="I18" t="str">
-        <v>HSN8017</v>
+        <v>401120</v>
       </c>
       <c r="J18" t="str">
-        <v>PROD-2026-1017</v>
+        <v>TYR-R20-16PR-HD</v>
       </c>
       <c r="K18" t="str">
-        <v>IndustrialBrand17</v>
+        <v>Apollo / MRF / BKT</v>
       </c>
       <c r="L18" t="str">
-        <v>MOD-PRO-17</v>
+        <v>LUG-PLUS-1000R20</v>
       </c>
       <c r="M18" t="str">
         <v>NEW</v>
@@ -1703,51 +1703,51 @@
         <v>Yes</v>
       </c>
       <c r="O18">
-        <v>3060</v>
-      </c>
-      <c r="P18" t="str">
-        <v/>
-      </c>
-      <c r="Q18" t="str">
-        <v/>
+        <v>25500</v>
+      </c>
+      <c r="P18">
+        <v>22800</v>
+      </c>
+      <c r="Q18">
+        <v>10.59</v>
       </c>
       <c r="R18" t="str">
-        <v>Special Offer</v>
+        <v>Mining Fleet Maintenance Price</v>
       </c>
       <c r="S18" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T18" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U18" t="str">
         <v>Yes</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W18" t="str">
-        <v>https://images.unsplash.com/photo-1581092795360-fd1ca04f0952, https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1581092335397-9583eb92d232</v>
+        <v>https://images.unsplash.com/photo-1517524008697-84bbe3c3fd98?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X18" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Premium Industrial Product Variant 18</v>
+        <v>Enterprise 2U Rackmount Server Dual Intel Xeon Silver 64GB ECC RAM</v>
       </c>
       <c r="B19" t="str">
-        <v>Gas Equipment &amp; Cylinders</v>
+        <v>IT &amp; Computer Equipment</v>
       </c>
       <c r="C19" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D19" t="str">
-        <v>High quality industrial product 18 with premium build. Ideal for heavy duty applications.</v>
+        <v>Mission-critical enterprise rack server configured with dual scalable Intel Xeon processors, redundant 80-Plus Platinum power supplies, and RAID controller.</v>
       </c>
       <c r="E19">
-        <v>2700</v>
+        <v>195000</v>
       </c>
       <c r="F19" t="str">
         <v>INR</v>
@@ -1759,69 +1759,69 @@
         <v>Nos</v>
       </c>
       <c r="I19" t="str">
-        <v>HSN8018</v>
+        <v>847150</v>
       </c>
       <c r="J19" t="str">
-        <v>PROD-2026-1018</v>
+        <v>IT-SRV-2U-XEON-64</v>
       </c>
       <c r="K19" t="str">
-        <v>IndustrialBrand18</v>
+        <v>Dell PowerEdge / HP ProLiant</v>
       </c>
       <c r="L19" t="str">
-        <v>MOD-PRO-18</v>
+        <v>PE-R750-XEON</v>
       </c>
       <c r="M19" t="str">
         <v>NEW</v>
       </c>
       <c r="N19" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O19">
-        <v>3240</v>
-      </c>
-      <c r="P19" t="str">
-        <v/>
-      </c>
-      <c r="Q19" t="str">
-        <v/>
+        <v>220000</v>
+      </c>
+      <c r="P19">
+        <v>195000</v>
+      </c>
+      <c r="Q19">
+        <v>11.36</v>
       </c>
       <c r="R19" t="str">
-        <v>Special Offer</v>
+        <v>Enterprise Digital Infrastructure Special</v>
       </c>
       <c r="S19" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T19" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U19" t="str">
         <v>Yes</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="W19" t="str">
-        <v>https://images.unsplash.com/photo-1530124566582-a618bc2615dc, https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1581092795360-fd1ca04f0952, https://images.unsplash.com/photo-1504917595217-d4dc5ebe6122</v>
+        <v>https://images.unsplash.com/photo-1558494949-ef010cbdcc31?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X19" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Premium Industrial Product Variant 19</v>
+        <v>Pneumatic Heavy Duty Industrial Air Impact Wrench (1-Inch Drive, 2600 Nm)</v>
       </c>
       <c r="B20" t="str">
-        <v>Agriculture &amp; Nursery</v>
+        <v>Tools &amp; Industrial Hardware</v>
       </c>
       <c r="C20" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D20" t="str">
-        <v>High quality industrial product 19 with premium build. Ideal for heavy duty applications.</v>
+        <v>Pin-less hammer mechanism air impact wrench delivering up to 2600 Nm break-away torque for heavy truck wheel lug nuts and heavy structural bolting.</v>
       </c>
       <c r="E20">
-        <v>2850</v>
+        <v>19500</v>
       </c>
       <c r="F20" t="str">
         <v>INR</v>
@@ -1833,16 +1833,16 @@
         <v>Nos</v>
       </c>
       <c r="I20" t="str">
-        <v>HSN8019</v>
+        <v>846711</v>
       </c>
       <c r="J20" t="str">
-        <v>PROD-2026-1019</v>
+        <v>TOOL-AIW-1IN-2600</v>
       </c>
       <c r="K20" t="str">
-        <v>IndustrialBrand19</v>
+        <v>Ingersoll Rand / Chicago Pneumatic</v>
       </c>
       <c r="L20" t="str">
-        <v>MOD-PRO-19</v>
+        <v>IR-2600-1IN</v>
       </c>
       <c r="M20" t="str">
         <v>NEW</v>
@@ -1851,51 +1851,51 @@
         <v>Yes</v>
       </c>
       <c r="O20">
-        <v>3420</v>
-      </c>
-      <c r="P20" t="str">
-        <v/>
-      </c>
-      <c r="Q20" t="str">
-        <v/>
+        <v>23000</v>
+      </c>
+      <c r="P20">
+        <v>19500</v>
+      </c>
+      <c r="Q20">
+        <v>15.22</v>
       </c>
       <c r="R20" t="str">
-        <v>Special Offer</v>
+        <v>Workshop Tooling Bundle</v>
       </c>
       <c r="S20" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T20" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U20" t="str">
         <v>Yes</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W20" t="str">
-        <v>https://images.unsplash.com/photo-1530124566582-a618bc2615dc, https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1504917595217-d4dc5ebe6122</v>
+        <v>https://images.unsplash.com/photo-1530124566582-a618bc2615dc?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X20" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/xfa_xobject.pdf</v>
+        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Premium Industrial Product Variant 20</v>
+        <v>Industrial PLC Automation Control Panel with 7-Inch Color Touch HMI</v>
       </c>
       <c r="B21" t="str">
-        <v>Industrial Seals &amp; Gaskets</v>
+        <v>Automation &amp; Robotics</v>
       </c>
       <c r="C21" t="str">
         <v>ACTIVE</v>
       </c>
       <c r="D21" t="str">
-        <v>High quality industrial product 20 with premium build. Ideal for heavy duty applications.</v>
+        <v>Custom-built IP65 electrical automation control desk panel incorporating programmable logic controller, variable frequency drives, SMPS, and safety relays.</v>
       </c>
       <c r="E21">
-        <v>3000</v>
+        <v>98000</v>
       </c>
       <c r="F21" t="str">
         <v>INR</v>
@@ -1904,19 +1904,19 @@
         <v>18</v>
       </c>
       <c r="H21" t="str">
-        <v>Nos</v>
+        <v>Set</v>
       </c>
       <c r="I21" t="str">
-        <v>HSN8020</v>
+        <v>853710</v>
       </c>
       <c r="J21" t="str">
-        <v>PROD-2026-1020</v>
+        <v>AUTO-PLC-PNL-7HMI</v>
       </c>
       <c r="K21" t="str">
-        <v>IndustrialBrand20</v>
+        <v>Siemens / Schneider MSME Integrator</v>
       </c>
       <c r="L21" t="str">
-        <v>MOD-PRO-20</v>
+        <v>S7-1200-HMI7</v>
       </c>
       <c r="M21" t="str">
         <v>NEW</v>
@@ -1925,34 +1925,34 @@
         <v>Yes</v>
       </c>
       <c r="O21">
-        <v>3600</v>
-      </c>
-      <c r="P21" t="str">
-        <v/>
-      </c>
-      <c r="Q21" t="str">
-        <v/>
+        <v>115000</v>
+      </c>
+      <c r="P21">
+        <v>98000</v>
+      </c>
+      <c r="Q21">
+        <v>14.78</v>
       </c>
       <c r="R21" t="str">
-        <v>Special Offer</v>
+        <v>Industrial Automation Promotion</v>
       </c>
       <c r="S21" t="str">
-        <v/>
+        <v>2026-09-01</v>
       </c>
       <c r="T21" t="str">
-        <v/>
+        <v>2026-12-31</v>
       </c>
       <c r="U21" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="W21" t="str">
-        <v>https://images.unsplash.com/photo-1581092335397-9583eb92d232, https://images.unsplash.com/photo-1581092160562-40aa08e11576, https://images.unsplash.com/photo-1581092795360-fd1ca04f0952, https://images.unsplash.com/photo-1581091226825-a6a2a5aee158</v>
+        <v>https://images.unsplash.com/photo-1581092580497-e0d23cbdf1dc?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X21" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf, https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
       </c>
     </row>
   </sheetData>
@@ -1964,7 +1964,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E88"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1985,16 +1985,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>PROD-2026-1001</v>
+        <v>STEEL-TMT-550D-12</v>
       </c>
       <c r="B2" t="str">
-        <v>Premium Industrial Product Variant 1</v>
+        <v>Fe 550D TMT Rebar (12mm x 12m Bundles)</v>
       </c>
       <c r="C2" t="str">
-        <v>Material</v>
+        <v>Grade</v>
       </c>
       <c r="D2" t="str">
-        <v>High-Grade Alloy Type 1</v>
+        <v>Fe 550D</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -2002,33 +2002,33 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>PROD-2026-1001</v>
+        <v>STEEL-TMT-550D-12</v>
       </c>
       <c r="B3" t="str">
-        <v>Premium Industrial Product Variant 1</v>
+        <v>Fe 550D TMT Rebar (12mm x 12m Bundles)</v>
       </c>
       <c r="C3" t="str">
-        <v>Weight</v>
+        <v>Diameter</v>
       </c>
       <c r="D3" t="str">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="E3" t="str">
-        <v>Kg</v>
+        <v>mm</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>PROD-2026-1001</v>
+        <v>STEEL-TMT-550D-12</v>
       </c>
       <c r="B4" t="str">
-        <v>Premium Industrial Product Variant 1</v>
+        <v>Fe 550D TMT Rebar (12mm x 12m Bundles)</v>
       </c>
       <c r="C4" t="str">
-        <v>Warranty</v>
+        <v>Standard</v>
       </c>
       <c r="D4" t="str">
-        <v>2 Years</v>
+        <v>IS 1786:2008</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -2036,84 +2036,84 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>PROD-2026-1001</v>
+        <v>STEEL-TMT-550D-12</v>
       </c>
       <c r="B5" t="str">
-        <v>Premium Industrial Product Variant 1</v>
+        <v>Fe 550D TMT Rebar (12mm x 12m Bundles)</v>
       </c>
       <c r="C5" t="str">
-        <v>Safety Standard</v>
+        <v>Yield Strength</v>
       </c>
       <c r="D5" t="str">
-        <v>ISO 9001:2015</v>
+        <v>550</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>N/mm²</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>PROD-2026-1002</v>
+        <v>STEEL-TMT-550D-12</v>
       </c>
       <c r="B6" t="str">
-        <v>Premium Industrial Product Variant 2</v>
+        <v>Fe 550D TMT Rebar (12mm x 12m Bundles)</v>
       </c>
       <c r="C6" t="str">
-        <v>Material</v>
+        <v>Elongation</v>
       </c>
       <c r="D6" t="str">
-        <v>High-Grade Alloy Type 2</v>
+        <v>14.5</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>%</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>PROD-2026-1002</v>
+        <v>SAF-HLM-PRO-E</v>
       </c>
       <c r="B7" t="str">
-        <v>Premium Industrial Product Variant 2</v>
+        <v>Industrial Safety Helmet Class-E with 6-Point Ratchet</v>
       </c>
       <c r="C7" t="str">
-        <v>Weight</v>
+        <v>Shell Material</v>
       </c>
       <c r="D7" t="str">
-        <v>3</v>
+        <v>High-Density Polyethylene (HDPE)</v>
       </c>
       <c r="E7" t="str">
-        <v>Kg</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>PROD-2026-1002</v>
+        <v>SAF-HLM-PRO-E</v>
       </c>
       <c r="B8" t="str">
-        <v>Premium Industrial Product Variant 2</v>
+        <v>Industrial Safety Helmet Class-E with 6-Point Ratchet</v>
       </c>
       <c r="C8" t="str">
-        <v>Warranty</v>
+        <v>Electrical Resistance</v>
       </c>
       <c r="D8" t="str">
-        <v>2 Years</v>
+        <v>20000</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>Volts</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>PROD-2026-1002</v>
+        <v>SAF-HLM-PRO-E</v>
       </c>
       <c r="B9" t="str">
-        <v>Premium Industrial Product Variant 2</v>
+        <v>Industrial Safety Helmet Class-E with 6-Point Ratchet</v>
       </c>
       <c r="C9" t="str">
-        <v>Safety Standard</v>
+        <v>Standard Certification</v>
       </c>
       <c r="D9" t="str">
-        <v>ISO 9001:2015</v>
+        <v>IS 2925:1984 / EN 397</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -2121,67 +2121,67 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>PROD-2026-1003</v>
+        <v>SAF-HLM-PRO-E</v>
       </c>
       <c r="B10" t="str">
-        <v>Premium Industrial Product Variant 3</v>
+        <v>Industrial Safety Helmet Class-E with 6-Point Ratchet</v>
       </c>
       <c r="C10" t="str">
-        <v>Material</v>
+        <v>Impact Energy Absorption</v>
       </c>
       <c r="D10" t="str">
-        <v>High-Grade Alloy Type 3</v>
+        <v>50</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>Joules</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PROD-2026-1003</v>
+        <v>VALV-BV-CS-100</v>
       </c>
       <c r="B11" t="str">
-        <v>Premium Industrial Product Variant 3</v>
+        <v>High-Pressure Carbon Steel Flanged Ball Valve (Class 300, 4-Inch)</v>
       </c>
       <c r="C11" t="str">
-        <v>Weight</v>
+        <v>Body Material</v>
       </c>
       <c r="D11" t="str">
-        <v>4.5</v>
+        <v>ASTM A216 Gr. WCB</v>
       </c>
       <c r="E11" t="str">
-        <v>Kg</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>PROD-2026-1003</v>
+        <v>VALV-BV-CS-100</v>
       </c>
       <c r="B12" t="str">
-        <v>Premium Industrial Product Variant 3</v>
+        <v>High-Pressure Carbon Steel Flanged Ball Valve (Class 300, 4-Inch)</v>
       </c>
       <c r="C12" t="str">
-        <v>Warranty</v>
+        <v>Nominal Size</v>
       </c>
       <c r="D12" t="str">
-        <v>2 Years</v>
+        <v>4</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>Inch</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>PROD-2026-1003</v>
+        <v>VALV-BV-CS-100</v>
       </c>
       <c r="B13" t="str">
-        <v>Premium Industrial Product Variant 3</v>
+        <v>High-Pressure Carbon Steel Flanged Ball Valve (Class 300, 4-Inch)</v>
       </c>
       <c r="C13" t="str">
-        <v>Safety Standard</v>
+        <v>Pressure Rating</v>
       </c>
       <c r="D13" t="str">
-        <v>ISO 9001:2015</v>
+        <v>Class 300 (PN 50)</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -2189,16 +2189,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>PROD-2026-1004</v>
+        <v>VALV-BV-CS-100</v>
       </c>
       <c r="B14" t="str">
-        <v>Premium Industrial Product Variant 4</v>
+        <v>High-Pressure Carbon Steel Flanged Ball Valve (Class 300, 4-Inch)</v>
       </c>
       <c r="C14" t="str">
-        <v>Material</v>
+        <v>End Connection</v>
       </c>
       <c r="D14" t="str">
-        <v>High-Grade Alloy Type 4</v>
+        <v>Flanged RF (ASME B16.5)</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -2206,101 +2206,101 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>PROD-2026-1004</v>
+        <v>VALV-BV-CS-100</v>
       </c>
       <c r="B15" t="str">
-        <v>Premium Industrial Product Variant 4</v>
+        <v>High-Pressure Carbon Steel Flanged Ball Valve (Class 300, 4-Inch)</v>
       </c>
       <c r="C15" t="str">
-        <v>Weight</v>
+        <v>Hydrostatic Shell Test</v>
       </c>
       <c r="D15" t="str">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="E15" t="str">
-        <v>Kg</v>
+        <v>Bar</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>PROD-2026-1004</v>
+        <v>MOT-IND-15HP-4P</v>
       </c>
       <c r="B16" t="str">
-        <v>Premium Industrial Product Variant 4</v>
+        <v>3-Phase Squirrel Cage Induction Motor (15 HP / 11 kW, 1440 RPM)</v>
       </c>
       <c r="C16" t="str">
-        <v>Warranty</v>
+        <v>Rated Output</v>
       </c>
       <c r="D16" t="str">
-        <v>2 Years</v>
+        <v>11</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>kW</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>PROD-2026-1004</v>
+        <v>MOT-IND-15HP-4P</v>
       </c>
       <c r="B17" t="str">
-        <v>Premium Industrial Product Variant 4</v>
+        <v>3-Phase Squirrel Cage Induction Motor (15 HP / 11 kW, 1440 RPM)</v>
       </c>
       <c r="C17" t="str">
-        <v>Safety Standard</v>
+        <v>Horsepower</v>
       </c>
       <c r="D17" t="str">
-        <v>ISO 9001:2015</v>
+        <v>15</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>HP</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>PROD-2026-1005</v>
+        <v>MOT-IND-15HP-4P</v>
       </c>
       <c r="B18" t="str">
-        <v>Premium Industrial Product Variant 5</v>
+        <v>3-Phase Squirrel Cage Induction Motor (15 HP / 11 kW, 1440 RPM)</v>
       </c>
       <c r="C18" t="str">
-        <v>Material</v>
+        <v>Speed</v>
       </c>
       <c r="D18" t="str">
-        <v>High-Grade Alloy Type 5</v>
+        <v>1440</v>
       </c>
       <c r="E18" t="str">
-        <v/>
+        <v>RPM</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>PROD-2026-1005</v>
+        <v>MOT-IND-15HP-4P</v>
       </c>
       <c r="B19" t="str">
-        <v>Premium Industrial Product Variant 5</v>
+        <v>3-Phase Squirrel Cage Induction Motor (15 HP / 11 kW, 1440 RPM)</v>
       </c>
       <c r="C19" t="str">
-        <v>Weight</v>
+        <v>Efficiency Class</v>
       </c>
       <c r="D19" t="str">
-        <v>7.5</v>
+        <v>IE3 Premium Efficiency</v>
       </c>
       <c r="E19" t="str">
-        <v>Kg</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PROD-2026-1005</v>
+        <v>MOT-IND-15HP-4P</v>
       </c>
       <c r="B20" t="str">
-        <v>Premium Industrial Product Variant 5</v>
+        <v>3-Phase Squirrel Cage Induction Motor (15 HP / 11 kW, 1440 RPM)</v>
       </c>
       <c r="C20" t="str">
-        <v>Warranty</v>
+        <v>Frame Size</v>
       </c>
       <c r="D20" t="str">
-        <v>2 Years</v>
+        <v>160M</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -2308,16 +2308,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PROD-2026-1005</v>
+        <v>MOT-IND-15HP-4P</v>
       </c>
       <c r="B21" t="str">
-        <v>Premium Industrial Product Variant 5</v>
+        <v>3-Phase Squirrel Cage Induction Motor (15 HP / 11 kW, 1440 RPM)</v>
       </c>
       <c r="C21" t="str">
-        <v>Safety Standard</v>
+        <v>Enclosure / IP Rating</v>
       </c>
       <c r="D21" t="str">
-        <v>ISO 9001:2015</v>
+        <v>IP55 Totally Enclosed Fan Cooled</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -2325,50 +2325,50 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>PROD-2026-1006</v>
+        <v>CBL-PWR-4C-185AL</v>
       </c>
       <c r="B22" t="str">
-        <v>Premium Industrial Product Variant 6</v>
+        <v>1.1 kV XLPE 4-Core Aluminium Armoured Power Cable (185 sq.mm)</v>
       </c>
       <c r="C22" t="str">
-        <v>Material</v>
+        <v>Voltage Rating</v>
       </c>
       <c r="D22" t="str">
-        <v>High-Grade Alloy Type 6</v>
+        <v>1100</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>V</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>PROD-2026-1006</v>
+        <v>CBL-PWR-4C-185AL</v>
       </c>
       <c r="B23" t="str">
-        <v>Premium Industrial Product Variant 6</v>
+        <v>1.1 kV XLPE 4-Core Aluminium Armoured Power Cable (185 sq.mm)</v>
       </c>
       <c r="C23" t="str">
-        <v>Weight</v>
+        <v>Cross Sectional Area</v>
       </c>
       <c r="D23" t="str">
-        <v>9</v>
+        <v>185</v>
       </c>
       <c r="E23" t="str">
-        <v>Kg</v>
+        <v>sq.mm</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>PROD-2026-1006</v>
+        <v>CBL-PWR-4C-185AL</v>
       </c>
       <c r="B24" t="str">
-        <v>Premium Industrial Product Variant 6</v>
+        <v>1.1 kV XLPE 4-Core Aluminium Armoured Power Cable (185 sq.mm)</v>
       </c>
       <c r="C24" t="str">
-        <v>Warranty</v>
+        <v>Conductor Material</v>
       </c>
       <c r="D24" t="str">
-        <v>2 Years</v>
+        <v>EC Grade Stranded Aluminium</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -2376,16 +2376,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PROD-2026-1006</v>
+        <v>CBL-PWR-4C-185AL</v>
       </c>
       <c r="B25" t="str">
-        <v>Premium Industrial Product Variant 6</v>
+        <v>1.1 kV XLPE 4-Core Aluminium Armoured Power Cable (185 sq.mm)</v>
       </c>
       <c r="C25" t="str">
-        <v>Safety Standard</v>
+        <v>Standard</v>
       </c>
       <c r="D25" t="str">
-        <v>ISO 9001:2015</v>
+        <v>IS 7098 (Part 1)</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -2393,16 +2393,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PROD-2026-1007</v>
+        <v>FAS-HEX-M16-80</v>
       </c>
       <c r="B26" t="str">
-        <v>Premium Industrial Product Variant 7</v>
+        <v>Grade 8.8 High-Tensile Hot-Dip Galvanized Hex Bolts &amp; Nuts (M16 x 80mm)</v>
       </c>
       <c r="C26" t="str">
-        <v>Material</v>
+        <v>Thread Size</v>
       </c>
       <c r="D26" t="str">
-        <v>High-Grade Alloy Type 7</v>
+        <v>M16 x 2.0mm</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -2410,33 +2410,33 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>PROD-2026-1007</v>
+        <v>FAS-HEX-M16-80</v>
       </c>
       <c r="B27" t="str">
-        <v>Premium Industrial Product Variant 7</v>
+        <v>Grade 8.8 High-Tensile Hot-Dip Galvanized Hex Bolts &amp; Nuts (M16 x 80mm)</v>
       </c>
       <c r="C27" t="str">
-        <v>Weight</v>
+        <v>Bolt Length</v>
       </c>
       <c r="D27" t="str">
-        <v>10.5</v>
+        <v>80</v>
       </c>
       <c r="E27" t="str">
-        <v>Kg</v>
+        <v>mm</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>PROD-2026-1007</v>
+        <v>FAS-HEX-M16-80</v>
       </c>
       <c r="B28" t="str">
-        <v>Premium Industrial Product Variant 7</v>
+        <v>Grade 8.8 High-Tensile Hot-Dip Galvanized Hex Bolts &amp; Nuts (M16 x 80mm)</v>
       </c>
       <c r="C28" t="str">
-        <v>Warranty</v>
+        <v>Property Class</v>
       </c>
       <c r="D28" t="str">
-        <v>2 Years</v>
+        <v>8.8</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -2444,16 +2444,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>PROD-2026-1007</v>
+        <v>FAS-HEX-M16-80</v>
       </c>
       <c r="B29" t="str">
-        <v>Premium Industrial Product Variant 7</v>
+        <v>Grade 8.8 High-Tensile Hot-Dip Galvanized Hex Bolts &amp; Nuts (M16 x 80mm)</v>
       </c>
       <c r="C29" t="str">
-        <v>Safety Standard</v>
+        <v>Coating</v>
       </c>
       <c r="D29" t="str">
-        <v>ISO 9001:2015</v>
+        <v>Hot Dip Galvanized (HDG &gt; 45 micron)</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -2461,186 +2461,186 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>PROD-2026-1008</v>
+        <v>BRG-DGB-6312-2RS</v>
       </c>
       <c r="B30" t="str">
-        <v>Premium Industrial Product Variant 8</v>
+        <v>Deep Groove Ball Bearing 6312-2RS1/C3 (60x130x31 mm)</v>
       </c>
       <c r="C30" t="str">
-        <v>Material</v>
+        <v>Bore Diameter (d)</v>
       </c>
       <c r="D30" t="str">
-        <v>High-Grade Alloy Type 8</v>
+        <v>60</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>mm</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>PROD-2026-1008</v>
+        <v>BRG-DGB-6312-2RS</v>
       </c>
       <c r="B31" t="str">
-        <v>Premium Industrial Product Variant 8</v>
+        <v>Deep Groove Ball Bearing 6312-2RS1/C3 (60x130x31 mm)</v>
       </c>
       <c r="C31" t="str">
-        <v>Weight</v>
+        <v>Outer Diameter (D)</v>
       </c>
       <c r="D31" t="str">
-        <v>12</v>
+        <v>130</v>
       </c>
       <c r="E31" t="str">
-        <v>Kg</v>
+        <v>mm</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>PROD-2026-1008</v>
+        <v>BRG-DGB-6312-2RS</v>
       </c>
       <c r="B32" t="str">
-        <v>Premium Industrial Product Variant 8</v>
+        <v>Deep Groove Ball Bearing 6312-2RS1/C3 (60x130x31 mm)</v>
       </c>
       <c r="C32" t="str">
-        <v>Warranty</v>
+        <v>Width (B)</v>
       </c>
       <c r="D32" t="str">
-        <v>2 Years</v>
+        <v>31</v>
       </c>
       <c r="E32" t="str">
-        <v/>
+        <v>mm</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>PROD-2026-1008</v>
+        <v>BRG-DGB-6312-2RS</v>
       </c>
       <c r="B33" t="str">
-        <v>Premium Industrial Product Variant 8</v>
+        <v>Deep Groove Ball Bearing 6312-2RS1/C3 (60x130x31 mm)</v>
       </c>
       <c r="C33" t="str">
-        <v>Safety Standard</v>
+        <v>Dynamic Load Rating</v>
       </c>
       <c r="D33" t="str">
-        <v>ISO 9001:2015</v>
+        <v>85.2</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>kN</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>PROD-2026-1009</v>
+        <v>BRG-DGB-6312-2RS</v>
       </c>
       <c r="B34" t="str">
-        <v>Premium Industrial Product Variant 9</v>
+        <v>Deep Groove Ball Bearing 6312-2RS1/C3 (60x130x31 mm)</v>
       </c>
       <c r="C34" t="str">
-        <v>Material</v>
+        <v>Limiting Speed</v>
       </c>
       <c r="D34" t="str">
-        <v>High-Grade Alloy Type 9</v>
+        <v>3800</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>RPM</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>PROD-2026-1009</v>
+        <v>HYD-CYL-100-400</v>
       </c>
       <c r="B35" t="str">
-        <v>Premium Industrial Product Variant 9</v>
+        <v>Double-Acting Heavy Duty Industrial Hydraulic Cylinder (100mm Bore x 400mm Stroke)</v>
       </c>
       <c r="C35" t="str">
-        <v>Weight</v>
+        <v>Bore Diameter</v>
       </c>
       <c r="D35" t="str">
-        <v>13.5</v>
+        <v>100</v>
       </c>
       <c r="E35" t="str">
-        <v>Kg</v>
+        <v>mm</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>PROD-2026-1009</v>
+        <v>HYD-CYL-100-400</v>
       </c>
       <c r="B36" t="str">
-        <v>Premium Industrial Product Variant 9</v>
+        <v>Double-Acting Heavy Duty Industrial Hydraulic Cylinder (100mm Bore x 400mm Stroke)</v>
       </c>
       <c r="C36" t="str">
-        <v>Warranty</v>
+        <v>Stroke Length</v>
       </c>
       <c r="D36" t="str">
-        <v>2 Years</v>
+        <v>400</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>mm</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>PROD-2026-1009</v>
+        <v>HYD-CYL-100-400</v>
       </c>
       <c r="B37" t="str">
-        <v>Premium Industrial Product Variant 9</v>
+        <v>Double-Acting Heavy Duty Industrial Hydraulic Cylinder (100mm Bore x 400mm Stroke)</v>
       </c>
       <c r="C37" t="str">
-        <v>Safety Standard</v>
+        <v>Operating Pressure</v>
       </c>
       <c r="D37" t="str">
-        <v>ISO 9001:2015</v>
+        <v>210</v>
       </c>
       <c r="E37" t="str">
-        <v/>
+        <v>Bar</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>PROD-2026-1010</v>
+        <v>HYD-CYL-100-400</v>
       </c>
       <c r="B38" t="str">
-        <v>Premium Industrial Product Variant 10</v>
+        <v>Double-Acting Heavy Duty Industrial Hydraulic Cylinder (100mm Bore x 400mm Stroke)</v>
       </c>
       <c r="C38" t="str">
-        <v>Material</v>
+        <v>Piston Rod Diameter</v>
       </c>
       <c r="D38" t="str">
-        <v>High-Grade Alloy Type 10</v>
+        <v>56</v>
       </c>
       <c r="E38" t="str">
-        <v/>
+        <v>mm</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>PROD-2026-1010</v>
+        <v>HYD-CYL-100-400</v>
       </c>
       <c r="B39" t="str">
-        <v>Premium Industrial Product Variant 10</v>
+        <v>Double-Acting Heavy Duty Industrial Hydraulic Cylinder (100mm Bore x 400mm Stroke)</v>
       </c>
       <c r="C39" t="str">
-        <v>Weight</v>
+        <v>Proof Pressure</v>
       </c>
       <c r="D39" t="str">
-        <v>15</v>
+        <v>315</v>
       </c>
       <c r="E39" t="str">
-        <v>Kg</v>
+        <v>Bar</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>PROD-2026-1010</v>
+        <v>CEM-PSC-50KG</v>
       </c>
       <c r="B40" t="str">
-        <v>Premium Industrial Product Variant 10</v>
+        <v>Portland Slag Cement (PSC) 50 Kg Moisture-Proof Bags</v>
       </c>
       <c r="C40" t="str">
-        <v>Warranty</v>
+        <v>Standard Conformance</v>
       </c>
       <c r="D40" t="str">
-        <v>2 Years</v>
+        <v>IS 455:2015</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -2648,203 +2648,203 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>PROD-2026-1010</v>
+        <v>CEM-PSC-50KG</v>
       </c>
       <c r="B41" t="str">
-        <v>Premium Industrial Product Variant 10</v>
+        <v>Portland Slag Cement (PSC) 50 Kg Moisture-Proof Bags</v>
       </c>
       <c r="C41" t="str">
-        <v>Safety Standard</v>
+        <v>Bag Weight</v>
       </c>
       <c r="D41" t="str">
-        <v>ISO 9001:2015</v>
+        <v>50</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>Kg</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>PROD-2026-1011</v>
+        <v>CEM-PSC-50KG</v>
       </c>
       <c r="B42" t="str">
-        <v>Premium Industrial Product Variant 11</v>
+        <v>Portland Slag Cement (PSC) 50 Kg Moisture-Proof Bags</v>
       </c>
       <c r="C42" t="str">
-        <v>Material</v>
+        <v>28-Day Compressive Strength</v>
       </c>
       <c r="D42" t="str">
-        <v>High-Grade Alloy Type 11</v>
+        <v>52</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>MPa</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>PROD-2026-1011</v>
+        <v>CEM-PSC-50KG</v>
       </c>
       <c r="B43" t="str">
-        <v>Premium Industrial Product Variant 11</v>
+        <v>Portland Slag Cement (PSC) 50 Kg Moisture-Proof Bags</v>
       </c>
       <c r="C43" t="str">
-        <v>Weight</v>
+        <v>Initial Setting Time</v>
       </c>
       <c r="D43" t="str">
-        <v>16.5</v>
+        <v>140</v>
       </c>
       <c r="E43" t="str">
-        <v>Kg</v>
+        <v>Minutes</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>PROD-2026-1011</v>
+        <v>WELD-INV-400A-3P</v>
       </c>
       <c r="B44" t="str">
-        <v>Premium Industrial Product Variant 11</v>
+        <v>IGBT Multi-Process Inverter Welding Machine (400 Amp, 3-Phase)</v>
       </c>
       <c r="C44" t="str">
-        <v>Warranty</v>
+        <v>Output Current Range</v>
       </c>
       <c r="D44" t="str">
-        <v>2 Years</v>
+        <v>20 - 400</v>
       </c>
       <c r="E44" t="str">
-        <v/>
+        <v>Amps</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>PROD-2026-1011</v>
+        <v>WELD-INV-400A-3P</v>
       </c>
       <c r="B45" t="str">
-        <v>Premium Industrial Product Variant 11</v>
+        <v>IGBT Multi-Process Inverter Welding Machine (400 Amp, 3-Phase)</v>
       </c>
       <c r="C45" t="str">
-        <v>Safety Standard</v>
+        <v>Input Voltage</v>
       </c>
       <c r="D45" t="str">
-        <v>ISO 9001:2015</v>
+        <v>415V ± 15% (3-Phase)</v>
       </c>
       <c r="E45" t="str">
-        <v/>
+        <v>V</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>PROD-2026-1012</v>
+        <v>WELD-INV-400A-3P</v>
       </c>
       <c r="B46" t="str">
-        <v>Premium Industrial Product Variant 12</v>
+        <v>IGBT Multi-Process Inverter Welding Machine (400 Amp, 3-Phase)</v>
       </c>
       <c r="C46" t="str">
-        <v>Material</v>
+        <v>Duty Cycle at 400A</v>
       </c>
       <c r="D46" t="str">
-        <v>High-Grade Alloy Type 12</v>
+        <v>60</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>%</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>PROD-2026-1012</v>
+        <v>WELD-INV-400A-3P</v>
       </c>
       <c r="B47" t="str">
-        <v>Premium Industrial Product Variant 12</v>
+        <v>IGBT Multi-Process Inverter Welding Machine (400 Amp, 3-Phase)</v>
       </c>
       <c r="C47" t="str">
-        <v>Weight</v>
+        <v>Usable Electrode Diameter</v>
       </c>
       <c r="D47" t="str">
-        <v>18</v>
+        <v>2.5 - 5.0</v>
       </c>
       <c r="E47" t="str">
-        <v>Kg</v>
+        <v>mm</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>PROD-2026-1012</v>
+        <v>REF-BRK-HA70-IS8</v>
       </c>
       <c r="B48" t="str">
-        <v>Premium Industrial Product Variant 12</v>
+        <v>High Alumina 70% Industrial Refractory Fire Bricks (IS 8 Standard)</v>
       </c>
       <c r="C48" t="str">
-        <v>Warranty</v>
+        <v>Alumina Content (Al2O3)</v>
       </c>
       <c r="D48" t="str">
-        <v>2 Years</v>
+        <v>70</v>
       </c>
       <c r="E48" t="str">
-        <v/>
+        <v>%</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>PROD-2026-1012</v>
+        <v>REF-BRK-HA70-IS8</v>
       </c>
       <c r="B49" t="str">
-        <v>Premium Industrial Product Variant 12</v>
+        <v>High Alumina 70% Industrial Refractory Fire Bricks (IS 8 Standard)</v>
       </c>
       <c r="C49" t="str">
-        <v>Safety Standard</v>
+        <v>Refractoriness (PCE)</v>
       </c>
       <c r="D49" t="str">
-        <v>ISO 9001:2015</v>
+        <v>+37 (&gt; 1820°C)</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>PCE</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>PROD-2026-1013</v>
+        <v>REF-BRK-HA70-IS8</v>
       </c>
       <c r="B50" t="str">
-        <v>Premium Industrial Product Variant 13</v>
+        <v>High Alumina 70% Industrial Refractory Fire Bricks (IS 8 Standard)</v>
       </c>
       <c r="C50" t="str">
-        <v>Material</v>
+        <v>Bulk Density</v>
       </c>
       <c r="D50" t="str">
-        <v>High-Grade Alloy Type 13</v>
+        <v>2.68</v>
       </c>
       <c r="E50" t="str">
-        <v/>
+        <v>g/cc</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>PROD-2026-1013</v>
+        <v>REF-BRK-HA70-IS8</v>
       </c>
       <c r="B51" t="str">
-        <v>Premium Industrial Product Variant 13</v>
+        <v>High Alumina 70% Industrial Refractory Fire Bricks (IS 8 Standard)</v>
       </c>
       <c r="C51" t="str">
-        <v>Weight</v>
+        <v>Cold Crushing Strength</v>
       </c>
       <c r="D51" t="str">
-        <v>19.5</v>
+        <v>650</v>
       </c>
       <c r="E51" t="str">
-        <v>Kg</v>
+        <v>kg/cm²</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PROD-2026-1013</v>
+        <v>SHG-SAM-SAREE-01</v>
       </c>
       <c r="B52" t="str">
-        <v>Premium Industrial Product Variant 13</v>
+        <v>Authentic Sambalpuri Handloom Pure Cotton Ikat Saree (GI Certified)</v>
       </c>
       <c r="C52" t="str">
-        <v>Warranty</v>
+        <v>Fabric</v>
       </c>
       <c r="D52" t="str">
-        <v>2 Years</v>
+        <v>100% Pure Organic Combed Cotton</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2852,16 +2852,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>PROD-2026-1013</v>
+        <v>SHG-SAM-SAREE-01</v>
       </c>
       <c r="B53" t="str">
-        <v>Premium Industrial Product Variant 13</v>
+        <v>Authentic Sambalpuri Handloom Pure Cotton Ikat Saree (GI Certified)</v>
       </c>
       <c r="C53" t="str">
-        <v>Safety Standard</v>
+        <v>Weave Pattern</v>
       </c>
       <c r="D53" t="str">
-        <v>ISO 9001:2015</v>
+        <v>Traditional Odisha Bandhakala (Ikat)</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2869,50 +2869,50 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PROD-2026-1014</v>
+        <v>SHG-SAM-SAREE-01</v>
       </c>
       <c r="B54" t="str">
-        <v>Premium Industrial Product Variant 14</v>
+        <v>Authentic Sambalpuri Handloom Pure Cotton Ikat Saree (GI Certified)</v>
       </c>
       <c r="C54" t="str">
-        <v>Material</v>
+        <v>Saree Length</v>
       </c>
       <c r="D54" t="str">
-        <v>High-Grade Alloy Type 14</v>
+        <v>6.3 (with Blouse Piece)</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>Meters</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PROD-2026-1014</v>
+        <v>SHG-SAM-SAREE-01</v>
       </c>
       <c r="B55" t="str">
-        <v>Premium Industrial Product Variant 14</v>
+        <v>Authentic Sambalpuri Handloom Pure Cotton Ikat Saree (GI Certified)</v>
       </c>
       <c r="C55" t="str">
-        <v>Weight</v>
+        <v>Origin Certification</v>
       </c>
       <c r="D55" t="str">
-        <v>21</v>
+        <v>Geographical Indication (GI) Tagged</v>
       </c>
       <c r="E55" t="str">
-        <v>Kg</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>PROD-2026-1014</v>
+        <v>SHG-DHK-FIG-08</v>
       </c>
       <c r="B56" t="str">
-        <v>Premium Industrial Product Variant 14</v>
+        <v>Odisha Dhokra Brass Lost-Wax Casting Tribal Art Figurine (8-Inch)</v>
       </c>
       <c r="C56" t="str">
-        <v>Warranty</v>
+        <v>Material</v>
       </c>
       <c r="D56" t="str">
-        <v>2 Years</v>
+        <v>Brass / Bronze Bell Metal Alloy</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2920,67 +2920,67 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>PROD-2026-1014</v>
+        <v>SHG-DHK-FIG-08</v>
       </c>
       <c r="B57" t="str">
-        <v>Premium Industrial Product Variant 14</v>
+        <v>Odisha Dhokra Brass Lost-Wax Casting Tribal Art Figurine (8-Inch)</v>
       </c>
       <c r="C57" t="str">
-        <v>Safety Standard</v>
+        <v>Height</v>
       </c>
       <c r="D57" t="str">
-        <v>ISO 9001:2015</v>
+        <v>8</v>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>Inch</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>PROD-2026-1015</v>
+        <v>SHG-DHK-FIG-08</v>
       </c>
       <c r="B58" t="str">
-        <v>Premium Industrial Product Variant 15</v>
+        <v>Odisha Dhokra Brass Lost-Wax Casting Tribal Art Figurine (8-Inch)</v>
       </c>
       <c r="C58" t="str">
-        <v>Material</v>
+        <v>Weight</v>
       </c>
       <c r="D58" t="str">
-        <v>High-Grade Alloy Type 15</v>
+        <v>1.1</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>Kg</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>PROD-2026-1015</v>
+        <v>SHG-DHK-FIG-08</v>
       </c>
       <c r="B59" t="str">
-        <v>Premium Industrial Product Variant 15</v>
+        <v>Odisha Dhokra Brass Lost-Wax Casting Tribal Art Figurine (8-Inch)</v>
       </c>
       <c r="C59" t="str">
-        <v>Weight</v>
+        <v>Craft Technique</v>
       </c>
       <c r="D59" t="str">
-        <v>22.5</v>
+        <v>Lost Wax Metal Casting (Cire Perdue)</v>
       </c>
       <c r="E59" t="str">
-        <v>Kg</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>PROD-2026-1015</v>
+        <v>SAF-GLV-NIT-15</v>
       </c>
       <c r="B60" t="str">
-        <v>Premium Industrial Product Variant 15</v>
+        <v>Industrial Heavy Duty Nitrile Chemical Gauntlet Gloves (15-Inch, 15 Mil)</v>
       </c>
       <c r="C60" t="str">
-        <v>Warranty</v>
+        <v>Material</v>
       </c>
       <c r="D60" t="str">
-        <v>2 Years</v>
+        <v>100% Acrylonitrile Butadiene</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2988,220 +2988,220 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>PROD-2026-1015</v>
+        <v>SAF-GLV-NIT-15</v>
       </c>
       <c r="B61" t="str">
-        <v>Premium Industrial Product Variant 15</v>
+        <v>Industrial Heavy Duty Nitrile Chemical Gauntlet Gloves (15-Inch, 15 Mil)</v>
       </c>
       <c r="C61" t="str">
-        <v>Safety Standard</v>
+        <v>Glove Length</v>
       </c>
       <c r="D61" t="str">
-        <v>ISO 9001:2015</v>
+        <v>15 (380mm)</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>Inch</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>PROD-2026-1016</v>
+        <v>SAF-GLV-NIT-15</v>
       </c>
       <c r="B62" t="str">
-        <v>Premium Industrial Product Variant 16</v>
+        <v>Industrial Heavy Duty Nitrile Chemical Gauntlet Gloves (15-Inch, 15 Mil)</v>
       </c>
       <c r="C62" t="str">
-        <v>Material</v>
+        <v>Thickness</v>
       </c>
       <c r="D62" t="str">
-        <v>High-Grade Alloy Type 16</v>
+        <v>15</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>Mil</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>PROD-2026-1016</v>
+        <v>SAF-GLV-NIT-15</v>
       </c>
       <c r="B63" t="str">
-        <v>Premium Industrial Product Variant 16</v>
+        <v>Industrial Heavy Duty Nitrile Chemical Gauntlet Gloves (15-Inch, 15 Mil)</v>
       </c>
       <c r="C63" t="str">
-        <v>Weight</v>
+        <v>Standard Rating</v>
       </c>
       <c r="D63" t="str">
-        <v>24</v>
+        <v>EN 388 (4101X) / EN ISO 374-1 Type A</v>
       </c>
       <c r="E63" t="str">
-        <v>Kg</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>PROD-2026-1016</v>
+        <v>CNV-BLT-EP400-800</v>
       </c>
       <c r="B64" t="str">
-        <v>Premium Industrial Product Variant 16</v>
+        <v>Heat-Resistant EP Rubber Conveyor Belt (EP 400/3, 800mm Wide)</v>
       </c>
       <c r="C64" t="str">
-        <v>Warranty</v>
+        <v>Belt Width</v>
       </c>
       <c r="D64" t="str">
-        <v>2 Years</v>
+        <v>800</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>mm</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>PROD-2026-1016</v>
+        <v>CNV-BLT-EP400-800</v>
       </c>
       <c r="B65" t="str">
-        <v>Premium Industrial Product Variant 16</v>
+        <v>Heat-Resistant EP Rubber Conveyor Belt (EP 400/3, 800mm Wide)</v>
       </c>
       <c r="C65" t="str">
-        <v>Safety Standard</v>
+        <v>Tensile Strength</v>
       </c>
       <c r="D65" t="str">
-        <v>ISO 9001:2015</v>
+        <v>400</v>
       </c>
       <c r="E65" t="str">
-        <v/>
+        <v>N/mm</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>PROD-2026-1017</v>
+        <v>CNV-BLT-EP400-800</v>
       </c>
       <c r="B66" t="str">
-        <v>Premium Industrial Product Variant 17</v>
+        <v>Heat-Resistant EP Rubber Conveyor Belt (EP 400/3, 800mm Wide)</v>
       </c>
       <c r="C66" t="str">
-        <v>Material</v>
+        <v>Number of Plies</v>
       </c>
       <c r="D66" t="str">
-        <v>High-Grade Alloy Type 17</v>
+        <v>3</v>
       </c>
       <c r="E66" t="str">
-        <v/>
+        <v>Plies</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>PROD-2026-1017</v>
+        <v>CNV-BLT-EP400-800</v>
       </c>
       <c r="B67" t="str">
-        <v>Premium Industrial Product Variant 17</v>
+        <v>Heat-Resistant EP Rubber Conveyor Belt (EP 400/3, 800mm Wide)</v>
       </c>
       <c r="C67" t="str">
-        <v>Weight</v>
+        <v>Temperature Rating</v>
       </c>
       <c r="D67" t="str">
-        <v>25.5</v>
+        <v>Up to 150°C continuous</v>
       </c>
       <c r="E67" t="str">
-        <v>Kg</v>
+        <v>°C</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>PROD-2026-1017</v>
+        <v>CNV-BLT-EP400-800</v>
       </c>
       <c r="B68" t="str">
-        <v>Premium Industrial Product Variant 17</v>
+        <v>Heat-Resistant EP Rubber Conveyor Belt (EP 400/3, 800mm Wide)</v>
       </c>
       <c r="C68" t="str">
-        <v>Warranty</v>
+        <v>Top / Bottom Rubber Cover</v>
       </c>
       <c r="D68" t="str">
-        <v>2 Years</v>
+        <v>5mm / 2mm Grade HR</v>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>mm</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>PROD-2026-1017</v>
+        <v>CHM-CS-FLK-50KG</v>
       </c>
       <c r="B69" t="str">
-        <v>Premium Industrial Product Variant 17</v>
+        <v>Technical Grade Caustic Soda Flakes / Sodium Hydroxide (99.5% Pure, 50kg)</v>
       </c>
       <c r="C69" t="str">
-        <v>Safety Standard</v>
+        <v>Assay (as NaOH)</v>
       </c>
       <c r="D69" t="str">
-        <v>ISO 9001:2015</v>
+        <v>99.5 Min</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>%</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>PROD-2026-1018</v>
+        <v>CHM-CS-FLK-50KG</v>
       </c>
       <c r="B70" t="str">
-        <v>Premium Industrial Product Variant 18</v>
+        <v>Technical Grade Caustic Soda Flakes / Sodium Hydroxide (99.5% Pure, 50kg)</v>
       </c>
       <c r="C70" t="str">
-        <v>Material</v>
+        <v>Sodium Carbonate (Na2CO3)</v>
       </c>
       <c r="D70" t="str">
-        <v>High-Grade Alloy Type 18</v>
+        <v>0.4 Max</v>
       </c>
       <c r="E70" t="str">
-        <v/>
+        <v>%</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>PROD-2026-1018</v>
+        <v>CHM-CS-FLK-50KG</v>
       </c>
       <c r="B71" t="str">
-        <v>Premium Industrial Product Variant 18</v>
+        <v>Technical Grade Caustic Soda Flakes / Sodium Hydroxide (99.5% Pure, 50kg)</v>
       </c>
       <c r="C71" t="str">
-        <v>Weight</v>
+        <v>Form</v>
       </c>
       <c r="D71" t="str">
-        <v>27</v>
+        <v>Dry White Deliquescent Flakes</v>
       </c>
       <c r="E71" t="str">
-        <v>Kg</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>PROD-2026-1018</v>
+        <v>CHM-CS-FLK-50KG</v>
       </c>
       <c r="B72" t="str">
-        <v>Premium Industrial Product Variant 18</v>
+        <v>Technical Grade Caustic Soda Flakes / Sodium Hydroxide (99.5% Pure, 50kg)</v>
       </c>
       <c r="C72" t="str">
-        <v>Warranty</v>
+        <v>Packaging</v>
       </c>
       <c r="D72" t="str">
-        <v>2 Years</v>
+        <v>50 Kg HDPE Laminated Bags with Liner</v>
       </c>
       <c r="E72" t="str">
-        <v/>
+        <v>Kg</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>PROD-2026-1018</v>
+        <v>TYR-R20-16PR-HD</v>
       </c>
       <c r="B73" t="str">
-        <v>Premium Industrial Product Variant 18</v>
+        <v>Heavy Duty Mining Dumper Radial Tyre (10.00 R20 16PR All-Steel)</v>
       </c>
       <c r="C73" t="str">
-        <v>Safety Standard</v>
+        <v>Tyre Size</v>
       </c>
       <c r="D73" t="str">
-        <v>ISO 9001:2015</v>
+        <v>10.00 R20</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3209,50 +3209,50 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>PROD-2026-1019</v>
+        <v>TYR-R20-16PR-HD</v>
       </c>
       <c r="B74" t="str">
-        <v>Premium Industrial Product Variant 19</v>
+        <v>Heavy Duty Mining Dumper Radial Tyre (10.00 R20 16PR All-Steel)</v>
       </c>
       <c r="C74" t="str">
-        <v>Material</v>
+        <v>Ply Rating</v>
       </c>
       <c r="D74" t="str">
-        <v>High-Grade Alloy Type 19</v>
+        <v>16</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>PR</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>PROD-2026-1019</v>
+        <v>TYR-R20-16PR-HD</v>
       </c>
       <c r="B75" t="str">
-        <v>Premium Industrial Product Variant 19</v>
+        <v>Heavy Duty Mining Dumper Radial Tyre (10.00 R20 16PR All-Steel)</v>
       </c>
       <c r="C75" t="str">
-        <v>Weight</v>
+        <v>Tread Depth</v>
       </c>
       <c r="D75" t="str">
-        <v>28.5</v>
+        <v>16.5</v>
       </c>
       <c r="E75" t="str">
-        <v>Kg</v>
+        <v>mm</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>PROD-2026-1019</v>
+        <v>TYR-R20-16PR-HD</v>
       </c>
       <c r="B76" t="str">
-        <v>Premium Industrial Product Variant 19</v>
+        <v>Heavy Duty Mining Dumper Radial Tyre (10.00 R20 16PR All-Steel)</v>
       </c>
       <c r="C76" t="str">
-        <v>Warranty</v>
+        <v>Speed Symbol / Load Index</v>
       </c>
       <c r="D76" t="str">
-        <v>2 Years</v>
+        <v>146/143 K (3000 kg/tyre)</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3260,16 +3260,16 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>PROD-2026-1019</v>
+        <v>IT-SRV-2U-XEON-64</v>
       </c>
       <c r="B77" t="str">
-        <v>Premium Industrial Product Variant 19</v>
+        <v>Enterprise 2U Rackmount Server Dual Intel Xeon Silver 64GB ECC RAM</v>
       </c>
       <c r="C77" t="str">
-        <v>Safety Standard</v>
+        <v>Processor</v>
       </c>
       <c r="D77" t="str">
-        <v>ISO 9001:2015</v>
+        <v>2x Intel Xeon Silver 4310 (24 Cores total)</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3277,50 +3277,50 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>PROD-2026-1020</v>
+        <v>IT-SRV-2U-XEON-64</v>
       </c>
       <c r="B78" t="str">
-        <v>Premium Industrial Product Variant 20</v>
+        <v>Enterprise 2U Rackmount Server Dual Intel Xeon Silver 64GB ECC RAM</v>
       </c>
       <c r="C78" t="str">
-        <v>Material</v>
+        <v>Memory</v>
       </c>
       <c r="D78" t="str">
-        <v>High-Grade Alloy Type 20</v>
+        <v>64GB (2x32GB) DDR4-3200 ECC RDIMM</v>
       </c>
       <c r="E78" t="str">
-        <v/>
+        <v>GB</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>PROD-2026-1020</v>
+        <v>IT-SRV-2U-XEON-64</v>
       </c>
       <c r="B79" t="str">
-        <v>Premium Industrial Product Variant 20</v>
+        <v>Enterprise 2U Rackmount Server Dual Intel Xeon Silver 64GB ECC RAM</v>
       </c>
       <c r="C79" t="str">
-        <v>Weight</v>
+        <v>Storage</v>
       </c>
       <c r="D79" t="str">
-        <v>30</v>
+        <v>2x 960GB Enterprise SAS Mixed-Use SSD</v>
       </c>
       <c r="E79" t="str">
-        <v>Kg</v>
+        <v>GB</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PROD-2026-1020</v>
+        <v>IT-SRV-2U-XEON-64</v>
       </c>
       <c r="B80" t="str">
-        <v>Premium Industrial Product Variant 20</v>
+        <v>Enterprise 2U Rackmount Server Dual Intel Xeon Silver 64GB ECC RAM</v>
       </c>
       <c r="C80" t="str">
-        <v>Warranty</v>
+        <v>RAID Controller</v>
       </c>
       <c r="D80" t="str">
-        <v>2 Years</v>
+        <v>Hardware PERC H745 with 4GB NV Cache</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3328,24 +3328,143 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>PROD-2026-1020</v>
+        <v>TOOL-AIW-1IN-2600</v>
       </c>
       <c r="B81" t="str">
-        <v>Premium Industrial Product Variant 20</v>
+        <v>Pneumatic Heavy Duty Industrial Air Impact Wrench (1-Inch Drive, 2600 Nm)</v>
       </c>
       <c r="C81" t="str">
-        <v>Safety Standard</v>
+        <v>Square Drive Size</v>
       </c>
       <c r="D81" t="str">
-        <v>ISO 9001:2015</v>
+        <v>1</v>
       </c>
       <c r="E81" t="str">
+        <v>Inch</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>TOOL-AIW-1IN-2600</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Pneumatic Heavy Duty Industrial Air Impact Wrench (1-Inch Drive, 2600 Nm)</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Max Working Torque</v>
+      </c>
+      <c r="D82" t="str">
+        <v>2600</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Nm</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>TOOL-AIW-1IN-2600</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Pneumatic Heavy Duty Industrial Air Impact Wrench (1-Inch Drive, 2600 Nm)</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Free Speed</v>
+      </c>
+      <c r="D83" t="str">
+        <v>4200</v>
+      </c>
+      <c r="E83" t="str">
+        <v>RPM</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>TOOL-AIW-1IN-2600</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Pneumatic Heavy Duty Industrial Air Impact Wrench (1-Inch Drive, 2600 Nm)</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Recommended Air Pressure</v>
+      </c>
+      <c r="D84" t="str">
+        <v>6.2 - 8.0</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Bar</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>AUTO-PLC-PNL-7HMI</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Industrial PLC Automation Control Panel with 7-Inch Color Touch HMI</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Main Controller</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Siemens Simatic S7-1200 CPU 1214C DC/DC/DC</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>AUTO-PLC-PNL-7HMI</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Industrial PLC Automation Control Panel with 7-Inch Color Touch HMI</v>
+      </c>
+      <c r="C86" t="str">
+        <v>HMI Touch Display</v>
+      </c>
+      <c r="D86" t="str">
+        <v>7 Inch 800x480 Widescreen 65K Colors</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>AUTO-PLC-PNL-7HMI</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Industrial PLC Automation Control Panel with 7-Inch Color Touch HMI</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Communication Protocol</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Profinet / Modbus TCP/IP</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>AUTO-PLC-PNL-7HMI</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Industrial PLC Automation Control Panel with 7-Inch Color Touch HMI</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Enclosure Protection</v>
+      </c>
+      <c r="D88" t="str">
+        <v>IP65 Powder Coated CRCA Steel 2mm</v>
+      </c>
+      <c r="E88" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E88"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3361,47 +3480,47 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Tyres &amp; Rubber Products</v>
+        <v>Agriculture &amp; Nursery</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Fuel, Oil &amp; Gas</v>
+        <v>Automation &amp; Robotics</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Power &amp; Energy Equipment</v>
+        <v>Automobile Parts &amp; Services</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Refractories</v>
+        <v>Bearings &amp; Mechanical Components</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Automobile Parts &amp; Services</v>
+        <v>Cement &amp; Concrete Products</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Office Equipment &amp; Stationery</v>
+        <v>Construction &amp; Building Materials</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Bearings &amp; Mechanical Components</v>
+        <v>Conveyor &amp; Material Handling Equipment</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Construction &amp; Building Materials</v>
+        <v>Electrical &amp; Electronics</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Steel &amp; Metal Products</v>
+        <v>Electrical Cables &amp; Power Equipment</v>
       </c>
     </row>
     <row r="11">
@@ -3411,52 +3530,52 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>teeeeeee</v>
+        <v>Fuel, Oil &amp; Gas</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Industrial Chemicals</v>
+        <v>Furniture &amp; Interior Supplies</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Electrical Cables &amp; Power Equipment</v>
+        <v>Gas Equipment &amp; Cylinders</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Industrial Consumables</v>
+        <v>General Industrial Supplier</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>IT &amp; Computer Equipment</v>
+        <v>Hydraulics &amp; Pneumatics</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Tools &amp; Industrial Hardware</v>
+        <v>IT &amp; Computer Equipment</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Furniture &amp; Interior Supplies</v>
+        <v>Industrial Chemicals</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>General Industrial Supplier</v>
+        <v>Industrial Consumables</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Gas Equipment &amp; Cylinders</v>
+        <v>Industrial Fasteners &amp; Components</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Agriculture &amp; Nursery</v>
+        <v>Industrial Machinery &amp; Spare Parts</v>
       </c>
     </row>
     <row r="22">
@@ -3466,7 +3585,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Industrial Fasteners &amp; Components</v>
+        <v>Laboratory Equipment &amp; Chemicals</v>
       </c>
     </row>
     <row r="24">
@@ -3481,7 +3600,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Pumps, Motors &amp; Hydraulics</v>
+        <v>Mining &amp; Coal Equipment</v>
       </c>
     </row>
     <row r="27">
@@ -3491,12 +3610,12 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Electrical &amp; Electronics</v>
+        <v>OEM / Manufacturing Vendor</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Pipes, Tiles &amp; Hardware</v>
+        <v>Office Equipment &amp; Stationery</v>
       </c>
     </row>
     <row r="30">
@@ -3506,42 +3625,42 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Safety Equipment &amp; Industrial Safety</v>
+        <v>Pipes, Tiles &amp; Hardware</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Cement &amp; Concrete Products</v>
+        <v>Polymer &amp; Plastic Products</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Textile &amp; Garments Supply</v>
+        <v>Power &amp; Energy Equipment</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>OEM / Manufacturing Vendor</v>
+        <v>Pumps, Motors &amp; Hydraulics</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Industrial Machinery &amp; Spare Parts</v>
+        <v>Refractories</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Automation &amp; Robotics</v>
+        <v>Retail &amp; Commercial Supply</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Polymer &amp; Plastic Products</v>
+        <v>Safety Equipment &amp; Industrial Safety</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Laboratory Equipment &amp; Chemicals</v>
+        <v>Steel &amp; Metal Products</v>
       </c>
     </row>
     <row r="39">
@@ -3551,27 +3670,27 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Mining &amp; Coal Equipment</v>
+        <v>Textile &amp; Garments Supply</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Hydraulics &amp; Pneumatics</v>
+        <v>Tools &amp; Industrial Hardware</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Welding &amp; Cutting Equipment</v>
+        <v>Tyres &amp; Rubber Products</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Retail &amp; Commercial Supply</v>
+        <v>Welding &amp; Cutting Equipment</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Conveyor &amp; Material Handling Equipment</v>
+        <v>test 1</v>
       </c>
     </row>
   </sheetData>

--- a/backend/seeded_templates/Seeded_Products_Import.xlsx
+++ b/backend/seeded_templates/Seeded_Products_Import.xlsx
@@ -546,7 +546,7 @@
         <v>https://images.unsplash.com/photo-1618090584176-7132b9911657?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X2" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="3">
@@ -694,7 +694,7 @@
         <v>https://images.unsplash.com/photo-1565043666747-69f6646db940?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X4" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="5">
@@ -842,7 +842,7 @@
         <v>https://images.unsplash.com/photo-1621905251189-08b45d6a269e?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X6" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="7">
@@ -913,7 +913,7 @@
         <v>500</v>
       </c>
       <c r="W7" t="str">
-        <v>https://images.unsplash.com/photo-1581092795360-fd1ca04f0952?w=1200&amp;auto=format&amp;fit=crop</v>
+        <v>https://images.unsplash.com/photo-1586864387967-d02ef85d93e8?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X7" t="str">
         <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/web/compressed.tracemonkey-pldi-09.pdf</v>
@@ -990,7 +990,7 @@
         <v>https://images.unsplash.com/photo-1581092334651-ddf26d9a09d0?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X8" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="9">
@@ -1138,7 +1138,7 @@
         <v>https://images.unsplash.com/photo-1587293852726-70cdb56c2866?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X10" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="11">
@@ -1286,7 +1286,7 @@
         <v>https://images.unsplash.com/photo-1587293852726-70cdb56c2866?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X12" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="13">
@@ -1434,7 +1434,7 @@
         <v>https://images.unsplash.com/photo-1590736704728-f4730bb30770?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X14" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="15">
@@ -1582,7 +1582,7 @@
         <v>https://images.unsplash.com/photo-1586528116311-ad8dd3c8310d?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X16" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="17">
@@ -1730,7 +1730,7 @@
         <v>https://images.unsplash.com/photo-1517524008697-84bbe3c3fd98?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X18" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="19">
@@ -1878,7 +1878,7 @@
         <v>https://images.unsplash.com/photo-1530124566582-a618bc2615dc?w=1200&amp;auto=format&amp;fit=crop</v>
       </c>
       <c r="X20" t="str">
-        <v>https://www.w3.org/WAI/ER/tests/xhtml/testfiles/resources/pdf/dummy.pdf</v>
+        <v>https://raw.githubusercontent.com/mozilla/pdf.js/ba2edeae/test/pdfs/basicapi.pdf</v>
       </c>
     </row>
     <row r="21">
